--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -17,14 +17,17 @@
     <sheet name="Comision" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Presupuesto" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Pruebas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Corfo" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gantt" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tareas'!$A$1:$J$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cambios'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tareas'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cambios'!$A$1:$E$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisiones'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Pendientes_dueño'!$A$1:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Riesgos'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Pruebas'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Corfo'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,9 +35,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red]-#,##0;-"/>
+    <numFmt numFmtId="166" formatCode="&quot;M&quot;0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -121,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,11 +165,17 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -184,6 +194,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="002E75B6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -619,7 +636,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tareas · Planner · Cambios · Decisiones · Pendientes_dueño · Riesgos · Comision (calculadora con fórmulas) · Presupuesto · Pruebas</t>
+          <t>Tareas · Planner · Cambios · Decisiones · Pendientes_dueño · Riesgos · Comision (calculadora con fórmulas) · Presupuesto · Pruebas · Corfo (requisitos de las bases) · Gantt (10 meses de ejecución)</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1539,1396 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Requisito</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Acción</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Postulante</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Persona natural mayor de 18 años y residente en Chile</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.1 a)</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Elegir al beneficiario entre los tres autores</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Postulante</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>No tener participación en una sociedad que ya ejecute el proyecto</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.1 a)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>No constituir la sociedad antes de postular</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Postulante</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>No figurar en el Registro Nacional de Deudores de Pensiones de Alimentos</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Bases 9.1, 13.3</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cada integrante lo revisa</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Postulante</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Sin otro proyecto Corfo vigente (más de 2 meses de terminar) ni cofinanciamiento previo del mismo emprendimiento</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.4</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar con cada integrante</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Postulante</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Una sola postulación por persona natural en cada convocatoria</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.4.2</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Postular una vez</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Innovación suficiente frente a las soluciones existentes</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Bases 2.1, 13.1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Estudio de competencia chilena y propuesta de valor</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Alcance no exclusivamente local (comunal o provincial no es admisible)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Bases 2.1 c)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Argumentar plan nacional con inicio en la Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>No tener ingresos por ventas (personas jurídicas) y primera venta durante la ejecución</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Bases 3, 4.1 b), 13.3</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Mantener el demo sin cobros reales</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Objetivo alineado: validación técnica y comercial (no compra de equipos ni consultorías)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Bases 2.1</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Redactar el plan de validación</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Al menos 2 personas (hasta 3 cofundadores) con roles complementarios</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.2, 9.2</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar roles y perfil comercial</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Dedicación horaria comprometida (máx. 40 a 44 h semanales) y verificable</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 d)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Completar horas por persona</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Participantes</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Entidad Patrocinadora de la nómina de Semilla Inicia habilitada para la región</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.3</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Buscar y elegir; preguntar a INACAP</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Participantes</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Mentoría de una red reconocida por Corfo, iniciada en los primeros 4 meses</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Bases 3, 7.1</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Elegir la red con la patrocinadora</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>a) Solución: problema, valor agregado, estado de desarrollo, ODS</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 a)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Completar docs/corfo/BORRADOR_POSTULACION.md</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>b) Escalabilidad: modelo de negocios, clientes, competencia, mercado, región</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 b)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Falta mercado y competencia chilena</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>c) Plan de validación con actividades y resultados</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 c)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Ajustar con fechas reales (hoja Gantt)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>d) Capacidades del equipo y dedicación</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 d)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Completar con datos reales</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>e) Video de máximo 40 s, accesible y con fecha de carga</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Bases 8 e)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Grabar con el guion del borrador</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Anexo 2 (ODS) y Anexo 3 (estrategia de operación sostenible)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Bases anexos 2 y 3</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Leer los anexos y completar</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Aporte propio de al menos 25 % del costo total</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Bases 6.3</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Completar la hoja Presupuesto</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Subsidio de hasta 75 % con tope de $15.000.000; gastos de inversión hasta 20 % del subsidio; honorarios de socios hasta $700.000 al mes (máx. 2)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Bases 6.1, 12</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Armar el presupuesto dentro de los topes</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Incluir la constitución de la sociedad e inicio de actividades (actividad obligatoria si es persona natural)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Bases 7.1 b)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Cotizar abogado y notaría</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Después de aprobar</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Contrato con la Entidad Patrocinadora y antecedentes de edad y residencia (15 días)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Bases 13.3, Anexo 1</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Después de aprobar</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Constituir la persona jurídica: beneficiario con participación mayoritaria; cada integrante con al menos 5 %</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Bases 4.4.2</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Acordar el reparto desde ya</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Fuente: bases técnicas de Semilla Inicia (Res. Exenta 1498/2025) y ficha oficial del concurso Biobío 2026. Cada convocatoria puede cambiar los requisitos: leer las bases del llamado exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D29" s="10">
+        <f>COUNTIF(E2:E25,"Cumple")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="D30" s="10">
+        <f>COUNTIF(E2:E25,"Por verificar")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Borrador</t>
+        </is>
+      </c>
+      <c r="D31" s="10">
+        <f>COUNTIF(E2:E25,"Borrador")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="D32" s="10">
+        <f>COUNTIF(E2:E25,"Falta")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="D33" s="10">
+        <f>COUNTIF(E2:E25,"Futuro")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G25"/>
+  <conditionalFormatting sqref="A2:G200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E2="Cumple"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>$E2="Borrador"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$E2="Por verificar"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$E2="Falta"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Cumple,Por verificar,Borrador,Falta,Futuro"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Inicio (mes)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Fin (mes)</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N1" s="23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Constituir la sociedad e iniciar actividades en el SII</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="26" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
+      <c r="M2" s="26" t="n"/>
+      <c r="N2" s="26" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Firmar el contrato con la Entidad Patrocinadora</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="26" t="n"/>
+      <c r="K3" s="26" t="n"/>
+      <c r="L3" s="26" t="n"/>
+      <c r="M3" s="26" t="n"/>
+      <c r="N3" s="26" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Definir el modelo de negocios con la mentoría</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="26" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="26" t="n"/>
+      <c r="K4" s="26" t="n"/>
+      <c r="L4" s="26" t="n"/>
+      <c r="M4" s="26" t="n"/>
+      <c r="N4" s="26" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Producción técnica: pasarela real, correo transaccional, T&amp;C, claves</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
+      <c r="H5" s="26" t="n"/>
+      <c r="I5" s="26" t="n"/>
+      <c r="J5" s="26" t="n"/>
+      <c r="K5" s="26" t="n"/>
+      <c r="L5" s="26" t="n"/>
+      <c r="M5" s="26" t="n"/>
+      <c r="N5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Cumplimiento Ley 21.719 y revisión legal</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="26" t="n"/>
+      <c r="L6" s="26" t="n"/>
+      <c r="M6" s="26" t="n"/>
+      <c r="N6" s="26" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Mentoría (debe iniciar antes del mes 4)</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="n"/>
+      <c r="N7" s="26" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Estrategia de operación sostenible (Anexo 3)</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="26" t="n"/>
+      <c r="N8" s="26" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Piloto con proveedores y clientes reales; validación comercial</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="26" t="n"/>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="26" t="n"/>
+      <c r="N9" s="26" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Primera venta: servicio pagado en la plataforma</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="26" t="n"/>
+      <c r="K10" s="26" t="n"/>
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="26" t="n"/>
+      <c r="N10" s="26" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Medición, ajustes y plan de escalamiento a otras regiones</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="26" t="n"/>
+      <c r="K11" s="26" t="n"/>
+      <c r="L11" s="26" t="n"/>
+      <c r="M11" s="26" t="n"/>
+      <c r="N11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Informe final y rendición</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="26" t="n"/>
+      <c r="N12" s="26" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Meses de ejecución desde la firma del convenio (máximo 10, más 2 de prórroga excepcional). Cambia el inicio y el fin (azul) y la barra se mueve sola. Cuando se conozca la fecha de apertura, pasa estas actividades a Planner con fechas reales.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:N32">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>AND($C2&lt;&gt;"",E$1&gt;=$C2,E$1&lt;=$D2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3099,12 +4499,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Corfo</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Corregir hallazgos de la revisión externa (Webpay doble confirmación, sesiones, cancelar/rechazar, eliminación con espera de 15 días, expiración de solicitudes)</t>
+          <t>Elegir al beneficiario (persona natural) y acordar el reparto de la futura sociedad entre los tres antes de postular</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -3114,24 +4514,24 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Dueño</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Si se aprueba hay que constituir la sociedad: el beneficiario debe tener participación mayoritaria y cada integrante al menos 5 %</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>plan-ajustes.md</t>
+          <t>docs/corfo/README.md</t>
         </is>
       </c>
     </row>
@@ -3143,12 +4543,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Corfo</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Invalidar access tokens al cambiar la clave o eliminar la cuenta; cerrar sesión en todos los dispositivos con código por correo</t>
+          <t>Buscar la Entidad Patrocinadora (nómina de Semilla Inicia de la región) y la red de mentores; preguntar a INACAP</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -3158,24 +4558,24 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Dueño</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Ambas son obligatorias en las bases</t>
+        </is>
+      </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+          <t>docs/corfo/README.md</t>
         </is>
       </c>
     </row>
@@ -3187,12 +4587,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Corfo</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Flow y Mercado Pago como medios de pago (código, probado con mocks)</t>
+          <t>Estudio de competencia chilena y tamaño de mercado con fuentes citables (la tesis solo compara con plataformas extranjeras)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -3202,28 +4602,24 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Dueño</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
+      <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Falta probar en sandbox real</t>
+          <t>Pesa en Innovación (40 %) y Escalabilidad (30 %)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+          <t>docs/corfo/DE_LA_TESIS_A_LA_POSTULACION.md</t>
         </is>
       </c>
     </row>
@@ -3235,39 +4631,39 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Corfo</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Registro de reembolsos, más avisos por correo, chequeos de claves inseguras</t>
+          <t>Completar el borrador de postulación: equipo, horas, ODS, sostenibilidad, metas de piloto</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Dueño</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Claude puede ayudar a redactar con tus datos</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+          <t>docs/corfo/BORRADOR_POSTULACION.md</t>
         </is>
       </c>
     </row>
@@ -3279,12 +4675,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Corfo</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Comisión por tramos que paga el cliente encima del precio + análisis de costos de pasarelas</t>
+          <t>Grabar el video de máximo 40 segundos (alojado con fecha de carga) y probar que abre sin clave</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3294,24 +4690,24 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Dueño</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Si no abre, la postulación no se evalúa</t>
+        </is>
+      </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>ANALISIS_COMISION.md</t>
+          <t>docs/corfo/BORRADOR_POSTULACION.md</t>
         </is>
       </c>
     </row>
@@ -3323,45 +4719,629 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>Corfo</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Vigilar la apertura de la próxima convocatoria de Semilla Inicia y leer las bases exactas de ese llamado</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Las de 2026 ya cerraron; no hay una abierta hoy</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>T-041</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Corfo</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>No cobrar dinero real ni constituir la sociedad antes de saber el resultado</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Persona jurídica sin ventas; la primera venta es parte de la ejecución</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Ley 21.719 (vigencia 1-dic-2026): ejecutar el plan de adecuación semana a semana</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Abogado</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Ver preguntas para el abogado en el plan</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>docs/cumplimiento/PLAN_ADECUACION_LEY_21719.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>T-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Contratos o DPA con los encargados y decisión sobre transferencias internacionales (EE. UU., Brasil)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Abogado</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>docs/cumplimiento/PLAN_ADECUACION_LEY_21719.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>T-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Simulacro de brecha de seguridad y de solicitud de derechos; designar suplente</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>docs/legal/protocolo-de-brechas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>T-045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Desarrollo</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Actualizar la EIPD y el registro de tratamientos con el video de verificación, Flow, Mercado Pago y los avisos por correo</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>docs/cumplimiento/PLAN_ADECUACION_LEY_21719.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>T-046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Desarrollo</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Armar la carta Gantt definitiva en Planner con fechas reales cuando se conozca la apertura</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Convocatoria abierta</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Hoja Gantt del Excel como base</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>hoja Gantt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>Hecho</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Corregir hallazgos de la revisión externa (Webpay doble confirmación, sesiones, cancelar/rechazar, eliminación con espera de 15 días, expiración de solicitudes)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>plan-ajustes.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Invalidar access tokens al cambiar la clave o eliminar la cuenta; cerrar sesión en todos los dispositivos con código por correo</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>T-049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Flow y Mercado Pago como medios de pago (código, probado con mocks)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Falta probar en sandbox real</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>T-050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Registro de reembolsos, más avisos por correo, chequeos de claves inseguras</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>T-051</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Comisión por tramos que paga el cliente encima del precio + análisis de costos de pasarelas</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>ANALISIS_COMISION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>T-052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Guía de postulación a Corfo con las bases oficiales (Semilla Inicia), borrador de postulación y puente tesis → postulación; plan de adecuación a la Ley 21.719</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Borradores a completar con tus datos</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>T-053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Verificación sin biometría con video + cédula revisada por un moderador (el video se borra al resolver)</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>Hecho</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0006</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J41"/>
-  <conditionalFormatting sqref="A2:J141">
+  <autoFilter ref="A1:J54"/>
+  <conditionalFormatting sqref="A2:J154">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="Hecho"</formula>
     </cfRule>
@@ -3373,13 +5353,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="D2:D141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,Bloqueado,Hecho"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dueño,Claude,Tercero"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3393,7 +5373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -4642,10 +6622,400 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5">
+        <f>Tareas!C42</f>
+        <v/>
+      </c>
+      <c r="B42" s="5">
+        <f>Tareas!B42</f>
+        <v/>
+      </c>
+      <c r="C42" s="5">
+        <f>IF(Tareas!E42="Hecho","Completada",IF(Tareas!E42="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>IF(Tareas!D42="Alta","Importante",IF(Tareas!D42="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E42" s="5">
+        <f>IF(Tareas!H42="","",Tareas!H42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>Tareas!F42</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>Tareas!I42</f>
+        <v/>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Se llena sola desde la hoja Tareas (filas 2 a 41). Si agregas tareas, copia las fórmulas hacia abajo.</t>
+      <c r="A43" s="5">
+        <f>Tareas!C43</f>
+        <v/>
+      </c>
+      <c r="B43" s="5">
+        <f>Tareas!B43</f>
+        <v/>
+      </c>
+      <c r="C43" s="5">
+        <f>IF(Tareas!E43="Hecho","Completada",IF(Tareas!E43="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D43" s="5">
+        <f>IF(Tareas!D43="Alta","Importante",IF(Tareas!D43="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E43" s="5">
+        <f>IF(Tareas!H43="","",Tareas!H43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="5">
+        <f>Tareas!F43</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>Tareas!I43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5">
+        <f>Tareas!C44</f>
+        <v/>
+      </c>
+      <c r="B44" s="5">
+        <f>Tareas!B44</f>
+        <v/>
+      </c>
+      <c r="C44" s="5">
+        <f>IF(Tareas!E44="Hecho","Completada",IF(Tareas!E44="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D44" s="5">
+        <f>IF(Tareas!D44="Alta","Importante",IF(Tareas!D44="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E44" s="5">
+        <f>IF(Tareas!H44="","",Tareas!H44)</f>
+        <v/>
+      </c>
+      <c r="F44" s="5">
+        <f>Tareas!F44</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>Tareas!I44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5">
+        <f>Tareas!C45</f>
+        <v/>
+      </c>
+      <c r="B45" s="5">
+        <f>Tareas!B45</f>
+        <v/>
+      </c>
+      <c r="C45" s="5">
+        <f>IF(Tareas!E45="Hecho","Completada",IF(Tareas!E45="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D45" s="5">
+        <f>IF(Tareas!D45="Alta","Importante",IF(Tareas!D45="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E45" s="5">
+        <f>IF(Tareas!H45="","",Tareas!H45)</f>
+        <v/>
+      </c>
+      <c r="F45" s="5">
+        <f>Tareas!F45</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>Tareas!I45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5">
+        <f>Tareas!C46</f>
+        <v/>
+      </c>
+      <c r="B46" s="5">
+        <f>Tareas!B46</f>
+        <v/>
+      </c>
+      <c r="C46" s="5">
+        <f>IF(Tareas!E46="Hecho","Completada",IF(Tareas!E46="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D46" s="5">
+        <f>IF(Tareas!D46="Alta","Importante",IF(Tareas!D46="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E46" s="5">
+        <f>IF(Tareas!H46="","",Tareas!H46)</f>
+        <v/>
+      </c>
+      <c r="F46" s="5">
+        <f>Tareas!F46</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>Tareas!I46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5">
+        <f>Tareas!C47</f>
+        <v/>
+      </c>
+      <c r="B47" s="5">
+        <f>Tareas!B47</f>
+        <v/>
+      </c>
+      <c r="C47" s="5">
+        <f>IF(Tareas!E47="Hecho","Completada",IF(Tareas!E47="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D47" s="5">
+        <f>IF(Tareas!D47="Alta","Importante",IF(Tareas!D47="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E47" s="5">
+        <f>IF(Tareas!H47="","",Tareas!H47)</f>
+        <v/>
+      </c>
+      <c r="F47" s="5">
+        <f>Tareas!F47</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>Tareas!I47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5">
+        <f>Tareas!C48</f>
+        <v/>
+      </c>
+      <c r="B48" s="5">
+        <f>Tareas!B48</f>
+        <v/>
+      </c>
+      <c r="C48" s="5">
+        <f>IF(Tareas!E48="Hecho","Completada",IF(Tareas!E48="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D48" s="5">
+        <f>IF(Tareas!D48="Alta","Importante",IF(Tareas!D48="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E48" s="5">
+        <f>IF(Tareas!H48="","",Tareas!H48)</f>
+        <v/>
+      </c>
+      <c r="F48" s="5">
+        <f>Tareas!F48</f>
+        <v/>
+      </c>
+      <c r="G48" s="5">
+        <f>Tareas!I48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5">
+        <f>Tareas!C49</f>
+        <v/>
+      </c>
+      <c r="B49" s="5">
+        <f>Tareas!B49</f>
+        <v/>
+      </c>
+      <c r="C49" s="5">
+        <f>IF(Tareas!E49="Hecho","Completada",IF(Tareas!E49="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D49" s="5">
+        <f>IF(Tareas!D49="Alta","Importante",IF(Tareas!D49="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E49" s="5">
+        <f>IF(Tareas!H49="","",Tareas!H49)</f>
+        <v/>
+      </c>
+      <c r="F49" s="5">
+        <f>Tareas!F49</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>Tareas!I49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5">
+        <f>Tareas!C50</f>
+        <v/>
+      </c>
+      <c r="B50" s="5">
+        <f>Tareas!B50</f>
+        <v/>
+      </c>
+      <c r="C50" s="5">
+        <f>IF(Tareas!E50="Hecho","Completada",IF(Tareas!E50="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D50" s="5">
+        <f>IF(Tareas!D50="Alta","Importante",IF(Tareas!D50="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E50" s="5">
+        <f>IF(Tareas!H50="","",Tareas!H50)</f>
+        <v/>
+      </c>
+      <c r="F50" s="5">
+        <f>Tareas!F50</f>
+        <v/>
+      </c>
+      <c r="G50" s="5">
+        <f>Tareas!I50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5">
+        <f>Tareas!C51</f>
+        <v/>
+      </c>
+      <c r="B51" s="5">
+        <f>Tareas!B51</f>
+        <v/>
+      </c>
+      <c r="C51" s="5">
+        <f>IF(Tareas!E51="Hecho","Completada",IF(Tareas!E51="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D51" s="5">
+        <f>IF(Tareas!D51="Alta","Importante",IF(Tareas!D51="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E51" s="5">
+        <f>IF(Tareas!H51="","",Tareas!H51)</f>
+        <v/>
+      </c>
+      <c r="F51" s="5">
+        <f>Tareas!F51</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>Tareas!I51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5">
+        <f>Tareas!C52</f>
+        <v/>
+      </c>
+      <c r="B52" s="5">
+        <f>Tareas!B52</f>
+        <v/>
+      </c>
+      <c r="C52" s="5">
+        <f>IF(Tareas!E52="Hecho","Completada",IF(Tareas!E52="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D52" s="5">
+        <f>IF(Tareas!D52="Alta","Importante",IF(Tareas!D52="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E52" s="5">
+        <f>IF(Tareas!H52="","",Tareas!H52)</f>
+        <v/>
+      </c>
+      <c r="F52" s="5">
+        <f>Tareas!F52</f>
+        <v/>
+      </c>
+      <c r="G52" s="5">
+        <f>Tareas!I52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5">
+        <f>Tareas!C53</f>
+        <v/>
+      </c>
+      <c r="B53" s="5">
+        <f>Tareas!B53</f>
+        <v/>
+      </c>
+      <c r="C53" s="5">
+        <f>IF(Tareas!E53="Hecho","Completada",IF(Tareas!E53="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D53" s="5">
+        <f>IF(Tareas!D53="Alta","Importante",IF(Tareas!D53="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E53" s="5">
+        <f>IF(Tareas!H53="","",Tareas!H53)</f>
+        <v/>
+      </c>
+      <c r="F53" s="5">
+        <f>Tareas!F53</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>Tareas!I53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5">
+        <f>Tareas!C54</f>
+        <v/>
+      </c>
+      <c r="B54" s="5">
+        <f>Tareas!B54</f>
+        <v/>
+      </c>
+      <c r="C54" s="5">
+        <f>IF(Tareas!E54="Hecho","Completada",IF(Tareas!E54="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D54" s="5">
+        <f>IF(Tareas!D54="Alta","Importante",IF(Tareas!D54="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E54" s="5">
+        <f>IF(Tareas!H54="","",Tareas!H54)</f>
+        <v/>
+      </c>
+      <c r="F54" s="5">
+        <f>Tareas!F54</f>
+        <v/>
+      </c>
+      <c r="G54" s="5">
+        <f>Tareas!I54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Se llena sola desde la hoja Tareas (filas 2 a 54). Si agregas tareas, copia las fórmulas hacia abajo.</t>
         </is>
       </c>
     </row>
@@ -4660,7 +7030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5755,15 +8125,38 @@
       </c>
       <c r="E47" s="5" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>c687bee</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Agrega comisión por tramos, verificación con video y tablero de seguimiento</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Cada fila es un commit de master (git log). Para ver el detalle: git show &lt;commit&gt;. Agrega notas a mano si hace falta.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -2928,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5336,6 +5336,182 @@
       <c r="J54" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>T-054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 1: medición de impacto (situación laboral, tipo de servicio, reparación evitó reemplazo, reporte_impacto)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Agregados con supresión de grupos &lt; 5; finalidad en política y registro de actividades</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Prompt de implementación Corfo 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>T-055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 2: calculadora gratuita de valorización (/calculadora, PDF/xlsx, plantillas, ItemPresupuesto extendido)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Pública sin cuenta; contador de uso anónimo</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Prompt de implementación Corfo 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>T-056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 3: boleta fase 1 (folio de boleta de honorarios, primera boleta)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Sin integración con el SII; KeyServ no emite boletas</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Prompt de implementación Corfo 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>T-057</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 4: vía sin historial (destacar cédula + video en registro y portada)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Copy honesto según ADR 0006</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Prompt de implementación Corfo 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -7012,10 +7188,130 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="5">
+        <f>Tareas!C55</f>
+        <v/>
+      </c>
+      <c r="B55" s="5">
+        <f>Tareas!B55</f>
+        <v/>
+      </c>
+      <c r="C55" s="5">
+        <f>IF(Tareas!E55="Hecho","Completada",IF(Tareas!E55="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D55" s="5">
+        <f>IF(Tareas!D55="Alta","Importante",IF(Tareas!D55="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E55" s="5">
+        <f>IF(Tareas!H55="","",Tareas!H55)</f>
+        <v/>
+      </c>
+      <c r="F55" s="5">
+        <f>Tareas!F55</f>
+        <v/>
+      </c>
+      <c r="G55" s="5">
+        <f>Tareas!I55</f>
+        <v/>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Se llena sola desde la hoja Tareas (filas 2 a 54). Si agregas tareas, copia las fórmulas hacia abajo.</t>
+      <c r="A56" s="5">
+        <f>Tareas!C56</f>
+        <v/>
+      </c>
+      <c r="B56" s="5">
+        <f>Tareas!B56</f>
+        <v/>
+      </c>
+      <c r="C56" s="5">
+        <f>IF(Tareas!E56="Hecho","Completada",IF(Tareas!E56="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D56" s="5">
+        <f>IF(Tareas!D56="Alta","Importante",IF(Tareas!D56="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E56" s="5">
+        <f>IF(Tareas!H56="","",Tareas!H56)</f>
+        <v/>
+      </c>
+      <c r="F56" s="5">
+        <f>Tareas!F56</f>
+        <v/>
+      </c>
+      <c r="G56" s="5">
+        <f>Tareas!I56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5">
+        <f>Tareas!C57</f>
+        <v/>
+      </c>
+      <c r="B57" s="5">
+        <f>Tareas!B57</f>
+        <v/>
+      </c>
+      <c r="C57" s="5">
+        <f>IF(Tareas!E57="Hecho","Completada",IF(Tareas!E57="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D57" s="5">
+        <f>IF(Tareas!D57="Alta","Importante",IF(Tareas!D57="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E57" s="5">
+        <f>IF(Tareas!H57="","",Tareas!H57)</f>
+        <v/>
+      </c>
+      <c r="F57" s="5">
+        <f>Tareas!F57</f>
+        <v/>
+      </c>
+      <c r="G57" s="5">
+        <f>Tareas!I57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5">
+        <f>Tareas!C58</f>
+        <v/>
+      </c>
+      <c r="B58" s="5">
+        <f>Tareas!B58</f>
+        <v/>
+      </c>
+      <c r="C58" s="5">
+        <f>IF(Tareas!E58="Hecho","Completada",IF(Tareas!E58="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D58" s="5">
+        <f>IF(Tareas!D58="Alta","Importante",IF(Tareas!D58="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E58" s="5">
+        <f>IF(Tareas!H58="","",Tareas!H58)</f>
+        <v/>
+      </c>
+      <c r="F58" s="5">
+        <f>Tareas!F58</f>
+        <v/>
+      </c>
+      <c r="G58" s="5">
+        <f>Tareas!I58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Se llena sola desde la hoja Tareas (filas 2 a 58). Si agregas tareas, copia las fórmulas hacia abajo.</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8675,6 +8971,166 @@
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>PLAN_FLUJO_DE_DINERO.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D-016</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre de la postulación: inclusión laboral y formalización, no antifraude</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/RESUMEN_PARA_PLANIFICACION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D-017</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Economía circular = reparar y mantener en vez de reemplazar; el ingreso que queda en la comuna se reporta aparte como "economía local"</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/RESUMEN_PARA_PLANIFICACION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>D-018</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Calculadora de valorización gratuita y abierta sin cuenta</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>D-019</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Boleta fase 1: el proveedor emite en sii.cl y KeyServ registra el folio; integración directa con el SII queda para después</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D-020</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ODS declarados: 8 (principal), 10 y 12. No se declaran el 5 ni el 16</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>docs/corfo/BORRADOR_POSTULACION.md</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -5371,10 +5371,14 @@
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Agregados con supresión de grupos &lt; 5; finalidad en política y registro de actividades</t>
+          <t>Migración 0044; ADR 0008; reporte_impacto; falta revisión legal de la finalidad (Pendientes_dueño)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -8463,7 +8467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9131,6 +9135,38 @@
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>docs/corfo/BORRADOR_POSTULACION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>D-021</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Medición de impacto: datos voluntarios (situación laboral previa, género), tipo de servicio y pregunta de reemplazo; reporte solo agregado con supresión de grupos &lt; 5 y sin cuentas demo</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Claude (técnica) / Dueño (estrategia)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>docs/adr/0008</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9470,6 +9506,29 @@
       </c>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Abogado: medición de impacto</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Revisar la finalidad escrita en el registro y en la política, la base de licitud (consentimiento voluntario y revocable), si situación laboral previa y género son dato sensible bajo la Ley 21.719 y el plazo de conservación</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>ADR 0008; registro-actividades-tratamiento.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E14"/>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -5410,7 +5410,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -5419,10 +5419,14 @@
         </is>
       </c>
       <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Pública sin cuenta; contador de uso anónimo</t>
+          <t>Migración 0045; ADR 0009; falta que un contador confirme la retención (Pendientes_dueño)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -8448,6 +8452,33 @@
       </c>
       <c r="E48" s="5" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>e20bfac</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Agrega medición de impacto: preguntas voluntarias, tipo de servicio y reporte agregado</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 1 (T-054)</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
@@ -8467,7 +8498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9167,6 +9198,38 @@
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>D-022</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Calculadora de valorización: el cálculo vive en el servidor (usa la comisión real), pesos enteros con boleta redondeada hacia arriba, exportación PDF/xlsx en el servidor, plantillas por cuenta, hoja de presupuesto extendida, contador anónimo con hash mensual</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Claude (técnica) / Dueño (estrategia)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>docs/adr/0009</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9527,6 +9590,52 @@
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>ADR 0008; registro-actividades-tratamiento.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contador: boleta de honorarios en la calculadora</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar la retención vigente (la calculadora usa 16 % para 2027, editable con CALCULADORA_RETENCION_BOLETA) y cómo van los materiales dentro de una boleta de honorarios</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>ADR 0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Abogado: contador anónimo de la calculadora</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar si el identificador aleatorio del navegador (hash mensual, sin IP ni cuenta) cuenta como dato personal y si basta con lo declarado en la política</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>ADR 0009; registro-actividades-tratamiento.md</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -5458,7 +5458,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -5467,10 +5467,14 @@
         </is>
       </c>
       <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin integración con el SII; KeyServ no emite boletas</t>
+          <t>Migración 0046; ADR 0010; el folio es declarado, no verificado con el SII</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -8480,9 +8484,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Cada fila es un commit de master (git log). Para ver el detalle: git show &lt;commit&gt;. Agrega notas a mano si hace falta.</t>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>b525d74</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Agrega la calculadora gratuita de valorización con boleta de honorarios</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 2 (T-055)</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9230,6 +9254,38 @@
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>D-023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Boleta fase 1: el proveedor registra el folio de un trabajo pagado (uno por contratación, no repetido por proveedor, una sola primera boleta); KeyServ no emite ni verifica; el folio se conserva al anonimizar la cuenta</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Claude (técnica) / Dueño (estrategia)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>docs/adr/0010</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9636,6 +9692,29 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>ADR 0009; registro-actividades-tratamiento.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Contador/abogado: boleta fase 2</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Antes de verificar el folio con el SII o emitir boletas desde KeyServ: tratamiento tributario de la comisión, si hace falta ser emisor autorizado y qué integración corresponde</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>ADR 0010; PLAN_FLUJO_DE_DINERO.md §4</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Completar docs/corfo/BORRADOR_POSTULACION.md</t>
+          <t>Reescribir con el encuadre de inclusión laboral y citar cifras reales de manage.py reporte_impacto (docs/corfo/README.md §6); completar docs/corfo/BORRADOR_POSTULACION.md</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -5515,10 +5515,14 @@
         </is>
       </c>
       <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Copy honesto según ADR 0006</t>
+          <t>Solo copy y presentación; se corrigió el aviso "0 fotos de tu rostro guardadas"; sigue pendiente la revisión legal del video y el documento</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -7338,7 +7342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8507,6 +8511,33 @@
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Bloque 2 (T-055)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>32e5bea</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Agrega el registro del folio de la boleta de honorarios (fase 1, sin SII)</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 3 (T-056)</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9286,6 +9317,38 @@
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>D-024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Vía sin historial: destacar la cédula + video en portada y registro, diciendo que es una revisión humana (no una consulta al Registro Civil); corregir el aviso "0 fotos de tu rostro guardadas"</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Claude (copy) / Dueño (estrategia)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>docs/adr/0006 (actualización 2026-10-23)</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -7342,7 +7342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8538,6 +8538,33 @@
       <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Bloque 3 (T-056)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>611ed94</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Destaca la vía sin historial (cédula y video) y corrige el aviso de fotos del rostro</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Bloque 4 (T-057)</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -2928,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5528,6 +5528,50 @@
       <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Prompt de implementación Corfo 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>T-058</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Calculadora guiada: asistente paso a paso con un pequeño guía de indicaciones (guion fijo, sin IA) y resultado simple con «Ver el detalle»</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Plan acordado 2026-10-23; ver ESTADO_Y_PROXIMOS_PASOS.md. Conservar modo Normal, confirmar con ?contratacion, plantillas y exportaciones</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -7324,13 +7368,46 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5">
+        <f>Tareas!C59</f>
+        <v/>
+      </c>
+      <c r="B59" s="5">
+        <f>Tareas!B59</f>
+        <v/>
+      </c>
+      <c r="C59" s="5">
+        <f>IF(Tareas!E59="Hecho","Completada",IF(Tareas!E59="En curso","En curso","No iniciada"))</f>
+        <v/>
+      </c>
+      <c r="D59" s="5">
+        <f>IF(Tareas!D59="Alta","Importante",IF(Tareas!D59="Media","Media","Baja"))</f>
+        <v/>
+      </c>
+      <c r="E59" s="5">
+        <f>IF(Tareas!H59="","",Tareas!H59)</f>
+        <v/>
+      </c>
+      <c r="F59" s="5">
+        <f>Tareas!F59</f>
+        <v/>
+      </c>
+      <c r="G59" s="5">
+        <f>Tareas!I59</f>
+        <v/>
+      </c>
+    </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Se llena sola desde la hoja Tareas (filas 2 a 58). Si agregas tareas, copia las fórmulas hacia abajo.</t>
-        </is>
-      </c>
-    </row>
+          <t>Se llena sola desde la hoja Tareas (filas 2 a 59). Si agregas tareas, copia las fórmulas hacia abajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8580,7 +8657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9376,6 +9453,70 @@
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>docs/adr/0006 (actualización 2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>D-025</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Calculadora: "Confirmar contratación" pasa por la calculadora del trabajo; imprevistos y ganancia opcionales; IVA solo como documento opcional (la boleta de honorarios no lleva IVA); la retención se explica como adelanto del impuesto a la renta</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Aprobada</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>docs/adr/0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>D-026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Calculadora guiada (pendiente de implementar): asistente por pasos con un pequeño guía de guion fijo, sin IA externa, y resultado simple con detalle plegable</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Dueño</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Propuesta</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>docs/ESTADO_Y_PROXIMOS_PASOS.md</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9888,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Confirmar la retención vigente (la calculadora usa 16 % para 2027, editable con CALCULADORA_RETENCION_BOLETA) y cómo van los materiales dentro de una boleta de honorarios</t>
+          <t>Confirmar la retención vigente (16 % para 2027, editable con CALCULADORA_RETENCION_BOLETA), quién la retiene cuando el cliente es una persona natural, cómo van los materiales dentro de una boleta de honorarios y el tratamiento del IVA (opción "documento con IVA", 19 %, CALCULADORA_IVA) incluido el crédito fiscal por materiales comprados con factura</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">

--- a/docs/seguimiento/KeyServ_Seguimiento.xlsx
+++ b/docs/seguimiento/KeyServ_Seguimiento.xlsx
@@ -2928,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -5563,13 +5563,65 @@
         </is>
       </c>
       <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Plan acordado 2026-10-23; ver ESTADO_Y_PROXIMOS_PASOS.md. Conservar modo Normal, confirmar con ?contratacion, plantillas y exportaciones</t>
+          <t>Hecho: asistente por pasos, guía de guion fijo, ayuda por inactividad, resultado en tres cifras y modo «Ver todo junto». Falta revisar en celular.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>T-059</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Header unificado en 18 páginas y exportación (PDF/xlsx) con logo y hoja de referencia de boleta</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>La hoja de boleta aclara que no es oficial (KeyServ no emite boletas ni verifica folios).</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>ESTADO_Y_PROXIMOS_PASOS.md</t>
         </is>
@@ -5609,7 +5661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -7405,9 +7457,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
